--- a/shucle_report/충북혁신도시/20260101_20260325/report_충북혁신도시_20260101_20260325.xlsx
+++ b/shucle_report/충북혁신도시/20260101_20260325/report_충북혁신도시_20260101_20260325.xlsx
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 13:09 | 차트: 119개</t>
+          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 14:48 | 차트: 119개</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>4.1명</t>
+          <t>3.9명</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>+0.8명</t>
+          <t>+0.9명</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>+19.1%</t>
+          <t>+21.7%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>증가</t>
+          <t>⚠ 증가</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>▲ 신규 지역 회원(일평균) (+19.1%)</t>
+          <t>▲ 신규 지역 회원(일평균) (+21.7%)</t>
         </is>
       </c>
     </row>
@@ -1902,27 +1902,27 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>8,342</t>
+          <t>8,067</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>8,740</t>
+          <t>8,636</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>+397.9</t>
+          <t>+568.9</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>+4.8%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>누적 8740명 (5% 증가)</t>
+          <t>누적 8636명 (7% 증가)</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>• 성장 지표 긍정적: 신규회원 4→5명(+19%), 누적 8937명 — 이용자 기반 확대 추세</t>
+          <t>• 성장 지표 긍정적: 신규회원 4→5명(+22%), 누적 8937명 — 이용자 기반 확대 추세</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2120,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>+5.9</t>
+          <t>+4.2</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>평일 66.9명 (10% 증가)</t>
+          <t>평일 47.8명 (10% 증가)</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-11.3</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>주말 56.6명 (17% 감소)</t>
+          <t>주말 16.2명 (17% 감소)</t>
         </is>
       </c>
     </row>
@@ -2349,17 +2349,17 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>평일 15.4분 (6% 감소)</t>
+          <t>평일 11.0분 (6% 감소)</t>
         </is>
       </c>
     </row>
@@ -2386,17 +2386,17 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>주말 10.3분 (35% 감소)</t>
+          <t>주말 2.9분 (35% 감소)</t>
         </is>
       </c>
     </row>
